--- a/college-posters/data/985_211院校总名单.xlsx
+++ b/college-posters/data/985_211院校总名单.xlsx
@@ -460,8 +460,8 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -557,12 +557,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -607,12 +607,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -1317,12 +1317,12 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -1789,12 +1789,12 @@
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>

--- a/college-posters/data/985_211院校总名单.xlsx
+++ b/college-posters/data/985_211院校总名单.xlsx
@@ -557,12 +557,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -607,12 +607,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -653,12 +653,12 @@
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -703,12 +703,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -937,12 +937,12 @@
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -1317,12 +1317,12 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -1459,12 +1459,12 @@
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -1789,12 +1789,12 @@
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -2069,12 +2069,12 @@
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>

--- a/college-posters/data/985_211院校总名单.xlsx
+++ b/college-posters/data/985_211院校总名单.xlsx
@@ -653,12 +653,12 @@
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -703,12 +703,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -799,12 +799,12 @@
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -937,12 +937,12 @@
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -1363,12 +1363,12 @@
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -1459,12 +1459,12 @@
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -1605,12 +1605,12 @@
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -1651,12 +1651,12 @@
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -1835,12 +1835,12 @@
       <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -1881,12 +1881,12 @@
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -2023,12 +2023,12 @@
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -2069,12 +2069,12 @@
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -2261,12 +2261,12 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>

--- a/college-posters/data/985_211院校总名单.xlsx
+++ b/college-posters/data/985_211院校总名单.xlsx
@@ -799,12 +799,12 @@
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -891,12 +891,12 @@
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -1363,12 +1363,12 @@
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -1605,12 +1605,12 @@
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -1651,12 +1651,12 @@
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1697,12 @@
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -1835,12 +1835,12 @@
       <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -1881,12 +1881,12 @@
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -2023,12 +2023,12 @@
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -2115,12 +2115,12 @@
       <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -2161,12 +2161,12 @@
       <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -2261,12 +2261,12 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -2307,12 +2307,12 @@
       <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -2353,12 +2353,12 @@
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>

--- a/college-posters/data/985_211院校总名单.xlsx
+++ b/college-posters/data/985_211院校总名单.xlsx
@@ -891,12 +891,12 @@
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1697,12 @@
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -2115,12 +2115,12 @@
       <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -2161,12 +2161,12 @@
       <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -2307,12 +2307,12 @@
       <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -2353,12 +2353,12 @@
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -2399,12 +2399,12 @@
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -2491,12 +2491,12 @@
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -3623,12 +3623,12 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -3761,12 +3761,12 @@
       <c r="H70" s="2" t="inlineStr"/>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -4041,12 +4041,12 @@
       <c r="H76" s="2" t="inlineStr"/>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -4091,12 +4091,12 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -4693,12 +4693,12 @@
       <c r="H90" s="2" t="inlineStr"/>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -4785,12 +4785,12 @@
       <c r="H92" s="2" t="inlineStr"/>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -5571,12 +5571,12 @@
       <c r="H109" s="2" t="inlineStr"/>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>

--- a/college-posters/data/985_211院校总名单.xlsx
+++ b/college-posters/data/985_211院校总名单.xlsx
@@ -2399,12 +2399,12 @@
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -2491,12 +2491,12 @@
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -2537,12 +2537,12 @@
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -2583,12 +2583,12 @@
       <c r="H45" s="2" t="inlineStr"/>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -3623,12 +3623,12 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -3761,12 +3761,12 @@
       <c r="H70" s="2" t="inlineStr"/>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -4041,12 +4041,12 @@
       <c r="H76" s="2" t="inlineStr"/>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -4091,12 +4091,12 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -4279,12 +4279,12 @@
       <c r="H81" s="2" t="inlineStr"/>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -4325,12 +4325,12 @@
       <c r="H82" s="2" t="inlineStr"/>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -4417,12 +4417,12 @@
       <c r="H84" s="2" t="inlineStr"/>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -4693,12 +4693,12 @@
       <c r="H90" s="2" t="inlineStr"/>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       <c r="H91" s="2" t="inlineStr"/>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -4785,12 +4785,12 @@
       <c r="H92" s="2" t="inlineStr"/>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -4831,12 +4831,12 @@
       <c r="H93" s="2" t="inlineStr"/>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -4923,12 +4923,12 @@
       <c r="H95" s="2" t="inlineStr"/>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -5245,12 +5245,12 @@
       <c r="H102" s="2" t="inlineStr"/>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -5571,12 +5571,12 @@
       <c r="H109" s="2" t="inlineStr"/>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>

--- a/college-posters/data/985_211院校总名单.xlsx
+++ b/college-posters/data/985_211院校总名单.xlsx
@@ -2537,12 +2537,12 @@
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -2583,12 +2583,12 @@
       <c r="H45" s="2" t="inlineStr"/>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -4279,12 +4279,12 @@
       <c r="H81" s="2" t="inlineStr"/>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -4325,12 +4325,12 @@
       <c r="H82" s="2" t="inlineStr"/>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -4417,12 +4417,12 @@
       <c r="H84" s="2" t="inlineStr"/>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       <c r="H91" s="2" t="inlineStr"/>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -4831,12 +4831,12 @@
       <c r="H93" s="2" t="inlineStr"/>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -4923,12 +4923,12 @@
       <c r="H95" s="2" t="inlineStr"/>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -5245,12 +5245,12 @@
       <c r="H102" s="2" t="inlineStr"/>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>

--- a/college-posters/data/985_211院校总名单.xlsx
+++ b/college-posters/data/985_211院校总名单.xlsx
@@ -2445,12 +2445,12 @@
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -3151,12 +3151,12 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -3945,12 +3945,12 @@
       <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -4187,12 +4187,12 @@
       <c r="H79" s="2" t="inlineStr"/>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -4233,12 +4233,12 @@
       <c r="H80" s="2" t="inlineStr"/>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -5015,12 +5015,12 @@
       <c r="H97" s="2" t="inlineStr"/>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -5199,12 +5199,12 @@
       <c r="H101" s="2" t="inlineStr"/>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -5433,12 +5433,12 @@
       <c r="H106" s="2" t="inlineStr"/>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       <c r="H108" s="2" t="inlineStr"/>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -5663,12 +5663,12 @@
       <c r="H111" s="2" t="inlineStr"/>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>

--- a/college-posters/data/985_211院校总名单.xlsx
+++ b/college-posters/data/985_211院校总名单.xlsx
@@ -2445,12 +2445,12 @@
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -2629,12 +2629,12 @@
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -3051,12 +3051,12 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -3101,12 +3101,12 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -3151,12 +3151,12 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -3201,12 +3201,12 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -3807,12 +3807,12 @@
       <c r="H71" s="2" t="inlineStr"/>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -3945,12 +3945,12 @@
       <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -4187,12 +4187,12 @@
       <c r="H79" s="2" t="inlineStr"/>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -4233,12 +4233,12 @@
       <c r="H80" s="2" t="inlineStr"/>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -4463,12 +4463,12 @@
       <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -4555,12 +4555,12 @@
       <c r="H87" s="2" t="inlineStr"/>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       <c r="H88" s="2" t="inlineStr"/>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -4647,12 +4647,12 @@
       <c r="H89" s="2" t="inlineStr"/>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -5015,12 +5015,12 @@
       <c r="H97" s="2" t="inlineStr"/>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       <c r="H98" s="2" t="inlineStr"/>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -5199,12 +5199,12 @@
       <c r="H101" s="2" t="inlineStr"/>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -5433,12 +5433,12 @@
       <c r="H106" s="2" t="inlineStr"/>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       <c r="H108" s="2" t="inlineStr"/>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -5663,12 +5663,12 @@
       <c r="H111" s="2" t="inlineStr"/>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>

--- a/college-posters/data/985_211院校总名单.xlsx
+++ b/college-posters/data/985_211院校总名单.xlsx
@@ -2629,12 +2629,12 @@
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -3051,12 +3051,12 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -3101,12 +3101,12 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -3201,12 +3201,12 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -3297,12 +3297,12 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -3343,12 +3343,12 @@
       <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -3389,12 +3389,12 @@
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -3807,12 +3807,12 @@
       <c r="H71" s="2" t="inlineStr"/>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -4463,12 +4463,12 @@
       <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       <c r="H86" s="2" t="inlineStr"/>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -4555,12 +4555,12 @@
       <c r="H87" s="2" t="inlineStr"/>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       <c r="H88" s="2" t="inlineStr"/>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -4647,12 +4647,12 @@
       <c r="H89" s="2" t="inlineStr"/>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       <c r="H96" s="2" t="inlineStr"/>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       <c r="H98" s="2" t="inlineStr"/>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -5107,12 +5107,12 @@
       <c r="H99" s="2" t="inlineStr"/>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -5153,12 +5153,12 @@
       <c r="H100" s="2" t="inlineStr"/>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -5387,12 +5387,12 @@
       <c r="H105" s="2" t="inlineStr"/>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       <c r="H110" s="2" t="inlineStr"/>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>

--- a/college-posters/data/985_211院校总名单.xlsx
+++ b/college-posters/data/985_211院校总名单.xlsx
@@ -3297,12 +3297,12 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -3343,12 +3343,12 @@
       <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -3389,12 +3389,12 @@
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -3435,12 +3435,12 @@
       <c r="H63" s="2" t="inlineStr"/>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -3527,12 +3527,12 @@
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -3669,12 +3669,12 @@
       <c r="H68" s="2" t="inlineStr"/>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -3715,12 +3715,12 @@
       <c r="H69" s="2" t="inlineStr"/>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       <c r="H86" s="2" t="inlineStr"/>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       <c r="H96" s="2" t="inlineStr"/>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -5107,12 +5107,12 @@
       <c r="H99" s="2" t="inlineStr"/>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -5153,12 +5153,12 @@
       <c r="H100" s="2" t="inlineStr"/>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -5387,12 +5387,12 @@
       <c r="H105" s="2" t="inlineStr"/>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -5479,12 +5479,12 @@
       <c r="H107" s="2" t="inlineStr"/>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       <c r="H110" s="2" t="inlineStr"/>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -5759,12 +5759,12 @@
       <c r="H113" s="2" t="inlineStr"/>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -5805,12 +5805,12 @@
       <c r="H114" s="2" t="inlineStr"/>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       <c r="H115" s="2" t="inlineStr"/>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -5897,12 +5897,12 @@
       <c r="H116" s="2" t="inlineStr"/>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>

--- a/college-posters/data/985_211院校总名单.xlsx
+++ b/college-posters/data/985_211院校总名单.xlsx
@@ -2675,12 +2675,12 @@
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -2721,12 +2721,12 @@
       <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -2813,12 +2813,12 @@
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -2859,12 +2859,12 @@
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -3001,12 +3001,12 @@
       <c r="H54" s="2" t="inlineStr"/>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -3435,12 +3435,12 @@
       <c r="H63" s="2" t="inlineStr"/>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -3527,12 +3527,12 @@
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -3669,12 +3669,12 @@
       <c r="H68" s="2" t="inlineStr"/>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -3715,12 +3715,12 @@
       <c r="H69" s="2" t="inlineStr"/>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -3853,12 +3853,12 @@
       <c r="H72" s="2" t="inlineStr"/>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -3899,12 +3899,12 @@
       <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -4371,12 +4371,12 @@
       <c r="H83" s="2" t="inlineStr"/>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -4877,12 +4877,12 @@
       <c r="H94" s="2" t="inlineStr"/>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -5341,12 +5341,12 @@
       <c r="H104" s="2" t="inlineStr"/>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -5479,12 +5479,12 @@
       <c r="H107" s="2" t="inlineStr"/>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -5759,12 +5759,12 @@
       <c r="H113" s="2" t="inlineStr"/>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -5805,12 +5805,12 @@
       <c r="H114" s="2" t="inlineStr"/>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       <c r="H115" s="2" t="inlineStr"/>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -5897,12 +5897,12 @@
       <c r="H116" s="2" t="inlineStr"/>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>

--- a/college-posters/data/985_211院校总名单.xlsx
+++ b/college-posters/data/985_211院校总名单.xlsx
@@ -1931,12 +1931,12 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -2675,12 +2675,12 @@
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -2721,12 +2721,12 @@
       <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -2767,12 +2767,12 @@
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -2813,12 +2813,12 @@
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -2859,12 +2859,12 @@
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -2905,12 +2905,12 @@
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -2955,12 +2955,12 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -3001,12 +3001,12 @@
       <c r="H54" s="2" t="inlineStr"/>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -3853,12 +3853,12 @@
       <c r="H72" s="2" t="inlineStr"/>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -3899,12 +3899,12 @@
       <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -3995,12 +3995,12 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>
@@ -4371,12 +4371,12 @@
       <c r="H83" s="2" t="inlineStr"/>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -4877,12 +4877,12 @@
       <c r="H94" s="2" t="inlineStr"/>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -5341,12 +5341,12 @@
       <c r="H104" s="2" t="inlineStr"/>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -5713,12 +5713,12 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>待收集</t>
+          <t>已收集（待审核）</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已出图（待审核）</t>
         </is>
       </c>
     </row>

--- a/college-posters/data/985_211院校总名单.xlsx
+++ b/college-posters/data/985_211院校总名单.xlsx
@@ -1931,12 +1931,12 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -2767,12 +2767,12 @@
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -2905,12 +2905,12 @@
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -2955,12 +2955,12 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -3995,12 +3995,12 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
@@ -5713,12 +5713,12 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>已收集（待审核）</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>已出图（待审核）</t>
+          <t>已出图</t>
         </is>
       </c>
     </row>
